--- a/erp-server/erp-server-dmp/src/main/resources/excel/platformInitStock.xlsx
+++ b/erp-server/erp-server-dmp/src/main/resources/excel/platformInitStock.xlsx
@@ -27,7 +27,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>核对仓库</t>
+    </r>
+  </si>
   <si>
     <r>
       <t>*</t>
@@ -45,13 +60,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -108,6 +116,9 @@
       </rPr>
       <t>期初数量</t>
     </r>
+  </si>
+  <si>
+    <t>安兔</t>
   </si>
   <si>
     <t>2025年09月</t>
@@ -736,11 +747,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1271,37 +1285,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="18.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.375" customWidth="1"/>
+    <col min="1" max="1" width="9.625" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
